--- a/Extracted_data_analysis/tropical/Output-Transformed_data/summary_counts_question_4.xlsx
+++ b/Extracted_data_analysis/tropical/Output-Transformed_data/summary_counts_question_4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t xml:space="preserve">meso_design</t>
   </si>
@@ -433,6 +433,9 @@
   </si>
   <si>
     <t xml:space="preserve">rugosity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rugosity+slope+turbidity</t>
   </si>
   <si>
     <t xml:space="preserve">salinity</t>
@@ -825,10 +828,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
@@ -1125,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -1155,10 +1158,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="33">
@@ -1221,10 +1224,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="39">
@@ -1353,10 +1356,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51">
@@ -1411,7 +1414,7 @@
         <v>8</v>
       </c>
       <c r="C55" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="56">
@@ -1749,10 +1752,10 @@
         <v>85</v>
       </c>
       <c r="B4" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C4" t="n">
-        <v>90.5</v>
+        <v>90.6</v>
       </c>
     </row>
   </sheetData>
@@ -1793,10 +1796,10 @@
         <v>84</v>
       </c>
       <c r="B3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C3" t="n">
-        <v>71.6</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="4">
@@ -1804,10 +1807,10 @@
         <v>85</v>
       </c>
       <c r="B4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C4" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
     </row>
   </sheetData>
@@ -1859,10 +1862,10 @@
         <v>90</v>
       </c>
       <c r="B4" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C4" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="5">
@@ -1873,7 +1876,7 @@
         <v>225</v>
       </c>
       <c r="C5" t="n">
-        <v>58.4</v>
+        <v>58.1</v>
       </c>
     </row>
   </sheetData>
@@ -2324,7 +2327,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="41">
@@ -2346,7 +2349,7 @@
         <v>224</v>
       </c>
       <c r="C42" t="n">
-        <v>58.2</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="43">
@@ -2442,10 +2445,10 @@
         <v>140</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="52">
@@ -2453,10 +2456,10 @@
         <v>141</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53">
@@ -2464,10 +2467,10 @@
         <v>142</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="54">
@@ -2475,10 +2478,10 @@
         <v>143</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2486,10 +2489,10 @@
         <v>144</v>
       </c>
       <c r="B55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="56">
@@ -2497,10 +2500,10 @@
         <v>145</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="57">
@@ -2508,10 +2511,10 @@
         <v>146</v>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="58">
@@ -2519,10 +2522,10 @@
         <v>147</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="59">
@@ -2541,10 +2544,10 @@
         <v>149</v>
       </c>
       <c r="B60" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="61">
@@ -2552,10 +2555,10 @@
         <v>150</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -2596,9 +2599,20 @@
         <v>154</v>
       </c>
       <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" t="n">
         <v>2</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C66" t="n">
         <v>0.5</v>
       </c>
     </row>
